--- a/修正内容報告_20260817-18.xlsx
+++ b/修正内容報告_20260817-18.xlsx
@@ -66,11 +66,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
@@ -82,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,25 +121,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -508,14 +508,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -540,453 +538,258 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>日付</t>
+          <t>カテゴリ</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>カテゴリ</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
           <t>変更内容</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>関連ファイル</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+    </row>
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>8/17</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>新機能／UI改善</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>完了工事一覧の詳細画面が「操業」「出張」の2タブから、通常画面と同じ「計画」「社内試運転」「出張」の3タブ構成に変更されました。完了した工事でも計画段階のタスクだけを分けて確認できるようになりました。</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>archive.js, index.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>新機能</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>・完了工事一覧に「計画」タブを追加し、通常画面と同じ3タブ構成に変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>8/17</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>その他（整理）</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>使い方ガイド（？ボタン）から、廃止された工事番号・機械・ユニット・担当者フィルターボタンの説明が削除されました（列見出しフィルターへの統合に伴う整理）。</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>auth.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>新機能</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>・表の列見出しにフィルター・並べ替え機能を追加（従来の絞り込みボタンは廃止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>新機能</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>画面上部にあった「工事番号」「機械」「ユニット」「担当者」の絞り込みボタンが廃止され、代わりに表の各列見出しにExcelのオートフィルターのような▼ボタンが付きました。▼を押すと、その列に実際に表示されている値の一覧からチェックで絞り込みができ、昇順・降順の並べ替えも選べます。開始日・完了予定日の列では年→月→日のツリー形式で選べます。絞り込み中の列は▼が漏斗マークに変わって一目で分かります。</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>index.html, data.js, gantt-setup.js, style.css</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>・担当別画面でバーをドラッグして移動・伸縮できるように改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>新機能</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>「担当別」表示画面で、担当者ごとの業務バーを直接ドラッグして期間を移動したり、バーの端をつまんで開始日・終了日を伸縮できるようになりました。ダブルクリックで詳細編集画面を開くことも可能です。</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>resource.js, style.css, gantt-setup.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>・表の列幅をドラッグで自由に調整できるように改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>UI改善</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>ガントチャートのバーや「担当別」画面のバーに、これまではタスク名だけだった表示が「工事番号 機械名 タスク名」とまとめて表示されるようになり、どの工事・機械の作業か一目で分かるようになりました。</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>gantt-setup.js, resource.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>・ガントバー・担当別バーの表示に工事番号・機械名を追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>不具合修正</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>表の「開始日」または「終了日」だけをその場で編集したときに、編集していないもう片方の日付まで勝手に変わってしまう不具合を修正しました。</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>gantt-setup.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>UI改善</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>・担当者プルダウンに「未定」を追加</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>不具合修正</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>「担当別」画面をフルスクリーン表示しているときに、スクロール位置がずれたりバーの座標がおかしくなって消えてしまう不具合を修正しました。</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>resource.js, gantt-setup.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>UI改善</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>・担当別画面の並び順を開始日順に変更し、機械名も表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>不具合修正</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>「担当別」フルスクリーン画面のタスクバーをダブルクリックしても編集画面が開かなかった不具合を修正し、担当別画面からも直接タスクを編集できるようになりました。</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>gantt-setup.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>UI改善</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>・タスク編集画面（ライトボックス）を拡大して見やすく改善</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>不具合修正</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>「＋新規タスク追加」ボタンを、工事番号を1件も選択していない状態でも、既存行の「＋」から使えば追加できるように修正しました（以前は工事番号を選んでいないと使えませんでした）。</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>gantt-setup.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>UI改善</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>・画面上部のボタン配置を整理</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>新機能</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>表の一部の列（ユニット・タスク名、出張モードでは客先・工事名）の幅を、境界線をドラッグして自由に変更できるようになりました。ダブルクリックすると内容に合わせて自動調整され、変更した幅は次回開いたときも保持されます。</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>gantt-setup.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>不具合修正</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>・開始日・終了日を個別編集すると他方まで変わってしまう不具合を修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>仕様変更（統合）</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>「🏭 現地試運転」という独立した表示モードが廃止され、「出張」モードに統合されました。出張タスクの中で「現地試運転」「現地SV」「調査」をプルダウンで選ぶ形になり、表示モードのボタンが1つ減ってシンプルになりました。またヘッダーの「📋 プログラム作成」ボタンの表記が「📋 計画」に変更されました。</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>index.html, data.js, gantt-setup.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>不具合修正</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>・担当別フルスクリーン表示の崩れを修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>仕様変更</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>表示モード（計画／社内試運転／出張）を切り替えるボタンについて、選択中のボタンをもう一度押しても「担当別」画面には戻らなくなりました（担当別画面に戻るには別の「👤担当別」ボタンを使う仕様に変更）。</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>data.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>不具合修正</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>・担当別フルスクリーンでダブルクリック編集ができない不具合を修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>UI改善</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>担当者プルダウンの選択肢に「未定」が追加され、担当者が決まっていないタスクにも登録しやすくなりました。</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>gantt-setup.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>不具合修正</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>・工事番号未選択でも新規タスクを追加できるよう修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>UI改善</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>「担当別」画面の担当者ごとの明細（タスク一覧）が、これまでの「計画→試運転→出張」という種類順の並びから、開始日が早い順の並びに変更されました（日付未定のタスクは末尾）。また各行に機械名も表示されるようになりました。</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>resource.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>仕様変更</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>・「現地試運転」モードを廃止し「出張」モードに統合</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>UI改善</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>タスクの編集画面（ライトボックス）が全体的に大きく見やすくなりました（幅・文字サイズ・入力欄の高さを拡大）。</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>style.css, gantt-setup.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>仕様変更</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>・表示モードボタンの再クリックで担当別画面に戻らない仕様に変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>UI改善</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>画面上部のボタン配置が整理され、「リソース表示」「＋新規タスク追加」「選択削除」「完了工事一覧」ボタンが表示モード切り替えボタンと同じ上段の行にまとめられました。またボタン群の間に区切り線が追加されました。</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>index.html, style.css</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>8/18</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>用語統一</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>「担当別」画面などの表記で「試運転」が「社内試運転」に統一され、他の画面と表現が揃いました。</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>resource.js, archive.js</t>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>・「試運転」の表記を「社内試運転」に統一</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -998,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1027,70 +830,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>新機能／UI改善</t>
+          <t>新機能</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>その他</t>
+          <t>UI改善</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>新機能</t>
+          <t>不具合修正</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UI改善</t>
+          <t>仕様変更</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>不具合修正</t>
+          <t>その他</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>仕様変更</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>用語統一</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
         <v>1</v>
       </c>
     </row>

--- a/修正内容報告_20260817-18.xlsx
+++ b/修正内容報告_20260817-18.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,23 +27,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="メイリオ"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="メイリオ"/>
       <i val="1"/>
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="メイリオ"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="メイリオ"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="メイリオ"/>
       <b val="1"/>
     </font>
   </fonts>
@@ -111,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -120,29 +128,30 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -828,52 +837,52 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>新機能</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>UI改善</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="13" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>不具合修正</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>仕様変更</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="13" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="13" t="n">
         <v>1</v>
       </c>
     </row>

--- a/修正内容報告_20260817-18.xlsx
+++ b/修正内容報告_20260817-18.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>・完了工事一覧に「計画」タブを追加し、通常画面と同じ3タブ構成に変更</t>
+          <t>完了工事一覧に「計画」タブを追加し、通常画面と同じ3タブ構成に変更</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>・表の列見出しにフィルター・並べ替え機能を追加（従来の絞り込みボタンは廃止）</t>
+          <t>表の列見出しにフィルター・並べ替え機能を追加（従来の絞り込みボタンは廃止）</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>・担当別画面でバーをドラッグして移動・伸縮できるように改善</t>
+          <t>担当別画面でバーをドラッグして移動・伸縮できるように改善</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>・表の列幅をドラッグで自由に調整できるように改善</t>
+          <t>表の列幅をドラッグで自由に調整できるように改善</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>・ガントバー・担当別バーの表示に工事番号・機械名を追加</t>
+          <t>ガントバー・担当別バーの表示に工事番号・機械名を追加</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>・担当者プルダウンに「未定」を追加</t>
+          <t>担当者プルダウンに「未定」を追加</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>・担当別画面の並び順を開始日順に変更し、機械名も表示</t>
+          <t>担当別画面の並び順を開始日順に変更し、機械名も表示</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>・タスク編集画面（ライトボックス）を拡大して見やすく改善</t>
+          <t>タスク編集画面（ライトボックス）を拡大して見やすく改善</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>・画面上部のボタン配置を整理</t>
+          <t>画面上部のボタン配置を整理</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>・開始日・終了日を個別編集すると他方まで変わってしまう不具合を修正</t>
+          <t>開始日・終了日を個別編集すると他方まで変わってしまう不具合を修正</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>・担当別フルスクリーン表示の崩れを修正</t>
+          <t>担当別フルスクリーン表示の崩れを修正</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>・担当別フルスクリーンでダブルクリック編集ができない不具合を修正</t>
+          <t>担当別フルスクリーンでダブルクリック編集ができない不具合を修正</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>・工事番号未選択でも新規タスクを追加できるよう修正</t>
+          <t>工事番号未選択でも新規タスクを追加できるよう修正</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>・「現地試運転」モードを廃止し「出張」モードに統合</t>
+          <t>「現地試運転」モードを廃止し「出張」モードに統合</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>・表示モードボタンの再クリックで担当別画面に戻らない仕様に変更</t>
+          <t>表示モードボタンの再クリックで担当別画面に戻らない仕様に変更</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>・「試運転」の表記を「社内試運転」に統一</t>
+          <t>「試運転」の表記を「社内試運転」に統一</t>
         </is>
       </c>
     </row>
